--- a/artfynd/A 71887-2021 artfynd.xlsx
+++ b/artfynd/A 71887-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 71887-2021 artfynd.xlsx
+++ b/artfynd/A 71887-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY12"/>
+  <dimension ref="A1:AY13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,53 +675,48 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>5049159</v>
+        <v>84982788</v>
       </c>
       <c r="B2" t="n">
-        <v>98519</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92699</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>222498</v>
+        <v>366</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Kandelabersvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Artomyces pyxidatus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Pers.) Jülich</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>1200 m NV om Larsro, Srm</t>
+          <t>Kärr, Srm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>635975.4922785092</v>
+        <v>635883</v>
       </c>
       <c r="R2" t="n">
-        <v>6517569.744677542</v>
+        <v>6517467</v>
       </c>
       <c r="S2" t="n">
-        <v>50</v>
+        <v>5</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -745,22 +740,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2009-08-03</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2019-11-15</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2009-08-03</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2019-11-15</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -771,36 +756,30 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
-      </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>betespräglad tallskog</t>
-        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Hans Rydberg</t>
+          <t>Ralf Lundmark</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Hans Rydberg</t>
-        </is>
-      </c>
-      <c r="AY2" t="inlineStr"/>
+          <t>Ralf Lundmark</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr">
+        <is>
+          <t>Kryptogamer i Södermanlands län</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>3381511</v>
+        <v>74825623</v>
       </c>
       <c r="B3" t="n">
-        <v>103177</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96458</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -808,37 +787,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221141</v>
+        <v>2818</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gullviva</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Primula veris</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>1200 m NV om Larsro, Srm</t>
+          <t>Hånö-Kärr, Srm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>635975.4922785092</v>
+        <v>635877</v>
       </c>
       <c r="R3" t="n">
-        <v>6517569.744677542</v>
+        <v>6517560</v>
       </c>
       <c r="S3" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -862,22 +841,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2009-08-03</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2018-09-12</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2009-08-03</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2018-09-12</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -888,36 +857,26 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
-      </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>betespräglad tallskog</t>
-        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Hans Rydberg</t>
+          <t>Markus Forsberg</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Hans Rydberg</t>
+          <t>Markus Forsberg</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>74825626</v>
+        <v>84982789</v>
       </c>
       <c r="B4" t="n">
-        <v>90074</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96458</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -925,46 +884,37 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>3298</v>
+        <v>2818</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Brid.) Z.Iwats.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Hånö-Kärr, Srm</t>
+          <t>Kärr, Srm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>635870.8887839634</v>
+        <v>635878</v>
       </c>
       <c r="R4" t="n">
-        <v>6517572.818442994</v>
+        <v>6517572</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -988,22 +938,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2018-09-12</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2019-11-15</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2018-09-12</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2019-11-15</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1018,27 +958,26 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Markus Forsberg</t>
+          <t>Ralf Lundmark</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Markus Forsberg</t>
-        </is>
-      </c>
-      <c r="AY4" t="inlineStr"/>
+          <t>Ralf Lundmark</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>Kryptogamer i Södermanlands län</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>74825625</v>
+        <v>74825626</v>
       </c>
       <c r="B5" t="n">
-        <v>5135</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92632</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1046,27 +985,31 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>105930</v>
+        <v>3298</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1075,10 +1018,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>635877.1643050417</v>
+        <v>635871</v>
       </c>
       <c r="R5" t="n">
-        <v>6517556.951575251</v>
+        <v>6517573</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1108,19 +1051,9 @@
           <t>2018-09-12</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2018-09-12</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1147,15 +1080,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>74825621</v>
+        <v>74825622</v>
       </c>
       <c r="B6" t="n">
-        <v>4717</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92567</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1163,34 +1091,43 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>102306</v>
+        <v>6031</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Blomkålssvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Sparassis crispa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(Wulfen:Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Hånö-Kärr, Srm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>635778.1134565037</v>
+        <v>635857</v>
       </c>
       <c r="R6" t="n">
-        <v>6517624.051674079</v>
+        <v>6517560</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1220,19 +1157,9 @@
           <t>2018-09-12</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2018-09-12</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1259,15 +1186,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>74825618</v>
+        <v>84982787</v>
       </c>
       <c r="B7" t="n">
-        <v>4717</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>44177</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1275,37 +1197,37 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>102306</v>
+        <v>101735</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Jättesvampmal</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Scardia boletella</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>(Fabricius, 1794)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Hånö-Kärr, Srm</t>
+          <t>Kärr, Srm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>635969.0379152392</v>
+        <v>635778</v>
       </c>
       <c r="R7" t="n">
-        <v>6517709.110210423</v>
+        <v>6517579</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1329,22 +1251,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2018-09-12</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2019-11-15</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2018-09-12</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2019-11-15</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1359,27 +1271,26 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Markus Forsberg</t>
+          <t>Ralf Lundmark</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Markus Forsberg</t>
-        </is>
-      </c>
-      <c r="AY7" t="inlineStr"/>
+          <t>Ralf Lundmark</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr">
+        <is>
+          <t>Kryptogamer i Södermanlands län</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>74825623</v>
+        <v>74825618</v>
       </c>
       <c r="B8" t="n">
-        <v>93158</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>4781</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1387,21 +1298,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>2818</v>
+        <v>102306</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1411,10 +1322,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>635877.0551628179</v>
+        <v>635969</v>
       </c>
       <c r="R8" t="n">
-        <v>6517560.061384213</v>
+        <v>6517709</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1444,19 +1355,9 @@
           <t>2018-09-12</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2018-09-12</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1483,37 +1384,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>74825619</v>
+        <v>74825620</v>
       </c>
       <c r="B9" t="n">
-        <v>89410</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>4781</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5432</v>
+        <v>102306</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1523,10 +1419,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>635969.0379152392</v>
+        <v>635881</v>
       </c>
       <c r="R9" t="n">
-        <v>6517709.110210423</v>
+        <v>6517733</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1556,19 +1452,9 @@
           <t>2018-09-12</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2018-09-12</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1595,53 +1481,48 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>84982788</v>
+        <v>74825621</v>
       </c>
       <c r="B10" t="n">
-        <v>90138</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>4781</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>366</v>
+        <v>102306</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Kandelabersvamp</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Artomyces pyxidatus</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Pers.) Jülich</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Kärr, Srm</t>
+          <t>Hånö-Kärr, Srm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>635883.4449681807</v>
+        <v>635778</v>
       </c>
       <c r="R10" t="n">
-        <v>6517466.875374788</v>
+        <v>6517624</v>
       </c>
       <c r="S10" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1665,22 +1546,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2019-11-15</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2018-09-12</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2019-11-15</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2018-09-12</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1695,31 +1566,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Ralf Lundmark</t>
+          <t>Markus Forsberg</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Ralf Lundmark</t>
-        </is>
-      </c>
-      <c r="AY10" t="inlineStr">
-        <is>
-          <t>Kryptogamer i Södermanlands län</t>
-        </is>
-      </c>
+          <t>Markus Forsberg</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>84982787</v>
+        <v>74825625</v>
       </c>
       <c r="B11" t="n">
-        <v>43464</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>5199</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1727,37 +1589,42 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>101735</v>
+        <v>105930</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Jättesvampmal</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Scardia boletella</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fabricius, 1794)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Kärr, Srm</t>
+          <t>Hånö-Kärr, Srm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>635778.11899246</v>
+        <v>635877</v>
       </c>
       <c r="R11" t="n">
-        <v>6517579.423625848</v>
+        <v>6517557</v>
       </c>
       <c r="S11" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1781,22 +1648,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2019-11-15</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2018-09-12</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2019-11-15</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2018-09-12</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1811,31 +1668,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Ralf Lundmark</t>
+          <t>Markus Forsberg</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Ralf Lundmark</t>
-        </is>
-      </c>
-      <c r="AY11" t="inlineStr">
-        <is>
-          <t>Kryptogamer i Södermanlands län</t>
-        </is>
-      </c>
+          <t>Markus Forsberg</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>84982789</v>
+        <v>3381511</v>
       </c>
       <c r="B12" t="n">
-        <v>93158</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106156</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1843,37 +1691,37 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>2818</v>
+        <v>221141</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Gullviva</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Primula veris</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Kärr, Srm</t>
+          <t>1200 m NV om Larsro, Srm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>635878.212690325</v>
+        <v>635975</v>
       </c>
       <c r="R12" t="n">
-        <v>6517571.518665905</v>
+        <v>6517570</v>
       </c>
       <c r="S12" t="n">
-        <v>5</v>
+        <v>50</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1897,22 +1745,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2019-11-15</t>
-        </is>
-      </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2009-08-03</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2019-11-15</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2009-08-03</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1923,23 +1761,126 @@
       </c>
       <c r="AG12" t="b">
         <v>0</v>
+      </c>
+      <c r="AI12" t="inlineStr">
+        <is>
+          <t>betespräglad tallskog</t>
+        </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Ralf Lundmark</t>
+          <t>Hans Rydberg</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Ralf Lundmark</t>
-        </is>
-      </c>
-      <c r="AY12" t="inlineStr">
-        <is>
-          <t>Kryptogamer i Södermanlands län</t>
-        </is>
-      </c>
+          <t>Hans Rydberg</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>5049159</v>
+      </c>
+      <c r="B13" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>1200 m NV om Larsro, Srm</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>635975</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6517570</v>
+      </c>
+      <c r="S13" t="n">
+        <v>50</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Nyköping</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Bälinge</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2009-08-03</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2009-08-03</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI13" t="inlineStr">
+        <is>
+          <t>betespräglad tallskog</t>
+        </is>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Hans Rydberg</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Hans Rydberg</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 71887-2021 artfynd.xlsx
+++ b/artfynd/A 71887-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY13"/>
+  <dimension ref="A1:AZ13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -773,6 +778,11 @@
           <t>Kryptogamer i Södermanlands län</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/84982788</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -870,6 +880,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/74825623</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -971,6 +986,11 @@
           <t>Kryptogamer i Södermanlands län</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/84982789</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1077,6 +1097,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/74825626</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1183,6 +1208,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/74825622</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1284,6 +1314,11 @@
           <t>Kryptogamer i Södermanlands län</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/84982787</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1381,6 +1416,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/74825618</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1478,6 +1518,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/74825620</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1575,6 +1620,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/74825621</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1677,6 +1727,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/74825625</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1779,6 +1834,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/3381511</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1881,8 +1941,27 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/5049159</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>